--- a/Result/profitability/2610.xlsx
+++ b/Result/profitability/2610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.68</v>
       </c>
       <c r="M2" t="n">
-        <v>0.485</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>16.625</v>
+        <v>15.80125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.79</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3075</v>
+        <v>0.2537499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>14.005</v>
+        <v>13.175</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06249999999999994</v>
+        <v>0.004999999999999949</v>
       </c>
       <c r="N4" t="n">
-        <v>12.1875</v>
+        <v>11.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-4.38</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.57125</v>
+        <v>-0.6212500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>11.3925</v>
+        <v>10.45</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.62</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7275</v>
+        <v>-0.7600000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>10.65125</v>
+        <v>10.0175</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7662500000000001</v>
+        <v>-0.8137500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>8.78875</v>
+        <v>7.92125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>-0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.0175</v>
       </c>
       <c r="N8" t="n">
-        <v>7.26</v>
+        <v>6.07625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.85125</v>
+        <v>-0.8512500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>7.795</v>
@@ -1772,7 +1772,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6512499999999999</v>
+        <v>-0.6512500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>10.645</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>63819</v>
+      </c>
+      <c r="D75" t="n">
+        <v>56716</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7102</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2665</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.18%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-365</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2300</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1413</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.59875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.29875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7294117647058823</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4597087378640776</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6349206349206349</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.540000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4038564542046064</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
